--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/auth-controller/logout-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/auth-controller/logout-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
-  <si>
-    <t>Statement: auth-controller.logout() – Server Action. Retrieves the current session via getSession() and calls session.destroy(). Returns { success: true, data: undefined }.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
+  <si>
+    <t>Statement: logout() – Destroys the current session cookie and returns an ActionResult&lt;void&gt;. Returns success with no data on success with the session destroyed. Returns a failure with a generic error message if session retrieval or session destruction fails unexpectedly.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>getSession is mock-injected; session.destroy is a jest.fn()</t>
+    <t>The session layer is available and supports destroy(). No authentication state is required to call logout.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;void&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;void&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Session is destroyed. Returns success=true.</t>
+    <t>On success: logout completes, session destroyed, no data returned. On failure: operation fails with generic error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,10 +64,16 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>session available</t>
-  </si>
-  <si>
-    <t>getSession resolves with { destroy: jest.fn() }</t>
+    <t>Session lifecycle</t>
+  </si>
+  <si>
+    <t>Session is retrieved and destroyed successfully → logout completes successfully, no data returned, session destroyed</t>
+  </si>
+  <si>
+    <t>Session retrieval fails unexpectedly → operation fails with generic error message</t>
+  </si>
+  <si>
+    <t>Session is retrieved, but destruction fails unexpectedly → operation fails with generic error message</t>
   </si>
   <si>
     <t>No TC</t>
@@ -85,13 +91,31 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>No input, session mock available</t>
-  </si>
-  <si>
-    <t>{ success: true }, session.destroy called</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>no input, session is retrieved and destroyed successfully</t>
+  </si>
+  <si>
+    <t>logout completes successfully, no data returned, session destroyed</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>no input, session retrieval fails unexpectedly</t>
+  </si>
+  <si>
+    <t>operation fails with generic error message</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>no input, session is retrieved, but session destruction fails unexpectedly</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -100,12 +124,6 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>No numerical input</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
@@ -115,15 +133,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>No input</t>
-  </si>
-  <si>
-    <t>success=true, session.destroy called</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -154,16 +163,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-03</t>
+    <t>CTRL-02</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -679,7 +685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -715,6 +721,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -723,7 +757,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -735,19 +769,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -755,16 +789,50 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -775,7 +843,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -785,24 +853,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -825,19 +882,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +905,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -861,22 +918,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -884,19 +941,59 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -924,16 +1021,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -941,45 +1038,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>45</v>
+      <c r="A3" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -988,19 +1085,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>48</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
